--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488301_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488301_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7114</v>
+        <v>0.7421</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8857</v>
+        <v>4.8424</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.1742</v>
+        <v>-4.1004</v>
       </c>
       <c r="G2" t="n">
         <v>1.9059</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7503</v>
+        <v>-0.7197</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0534</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6969</v>
+        <v>-0.623</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6294</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="G3" t="n">
         <v>0.1306</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>A. HERNANDEZ RAMOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.9924</v>
+        <v>-2.3129</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7959</v>
+        <v>-1.7552</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.7883</v>
+        <v>-0.5577</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.0082</v>
+        <v>-1.3318</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1021</v>
+        <v>0.1735</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.1103</v>
+        <v>-1.5053</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7312</v>
+        <v>-0.6099</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1767</v>
+        <v>0.0429</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4455</v>
+        <v>-0.6529</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.7394</v>
+        <v>-0.7219</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0745</v>
+        <v>0.1306</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.6648</v>
+        <v>-0.8524</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7411</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3864</v>
+        <v>-0.0547</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2146</v>
+        <v>-0.2189</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8282</v>
+        <v>0.1641</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. HERNANDEZ RAMOS</t>
+          <t>S. TRUJILLO SUAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.4114</v>
+        <v>-2.9614</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7552</v>
+        <v>-1.4635</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6562</v>
+        <v>-1.498</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3318</v>
+        <v>-3.1622</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1735</v>
+        <v>-3.0025</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5053</v>
+        <v>-0.1597</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6099</v>
+        <v>0.2346</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0429</v>
+        <v>-0.4811</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6529</v>
+        <v>0.7157</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7219</v>
+        <v>-3.3968</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1306</v>
+        <v>-2.5214</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8524</v>
+        <v>-0.8754</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1532</v>
+        <v>-0.7987</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2189</v>
+        <v>-0.4741</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06569999999999999</v>
+        <v>-0.3246</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. TRUJILLO SUAREZ</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.648</v>
+        <v>-3.4133</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9531</v>
+        <v>-0.3156</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6949</v>
+        <v>-3.0977</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1622</v>
+        <v>-6.853</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.0025</v>
+        <v>-1.6765</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1597</v>
+        <v>-5.1765</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2346</v>
+        <v>-2.4906</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4811</v>
+        <v>1.2192</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7157</v>
+        <v>-3.7098</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3968</v>
+        <v>-4.3624</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.5214</v>
+        <v>-2.8957</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8754</v>
+        <v>-1.4667</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3706</v>
+        <v>1.8529</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2234</v>
+        <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4853</v>
+        <v>-0.3009</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9637</v>
+        <v>0.2873</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5215</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6289</v>
+        <v>1.8877</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6289</v>
+        <v>1.8877</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>O. FAJANA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.712</v>
+        <v>-4.0388</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7621</v>
+        <v>-2.7881</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.95</v>
+        <v>-1.2507</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.853</v>
+        <v>0.0272</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6765</v>
+        <v>-0.6778</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.1765</v>
+        <v>0.705</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4906</v>
+        <v>1.4976</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2192</v>
+        <v>0.8542</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.7098</v>
+        <v>0.6434</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.3624</v>
+        <v>-1.4704</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.8957</v>
+        <v>-1.532</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4667</v>
+        <v>0.0616</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8529</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5996</v>
+        <v>-0.139</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1591</v>
+        <v>0.0501</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4405</v>
+        <v>-0.189</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8877</v>
+        <v>-1.8888</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8877</v>
+        <v>-0.63</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. FAJANA</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.5574</v>
+        <v>-4.27</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5283</v>
+        <v>0.6414</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0291</v>
+        <v>-4.9114</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0272</v>
+        <v>-3.0082</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6778</v>
+        <v>0.1021</v>
       </c>
       <c r="I8" t="n">
-        <v>0.705</v>
+        <v>-3.1103</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4976</v>
+        <v>1.7312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8542</v>
+        <v>2.1767</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6434</v>
+        <v>-0.4455</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4704</v>
+        <v>-4.7394</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.532</v>
+        <v>-2.0745</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0616</v>
+        <v>-2.6648</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0382</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.7057</v>
+        <v>-2.7793</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6576</v>
+        <v>0.1088</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6901</v>
+        <v>1.0601</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0326</v>
+        <v>-0.9513</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8888</v>
+        <v>-0.6294</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.63</v>
+        <v>0.6294</v>
       </c>
       <c r="X8" t="n">
         <v>-1.2589</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.8274</v>
+        <v>-6.161</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.4927</v>
+        <v>-3.7525</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3346</v>
+        <v>-2.4085</v>
       </c>
       <c r="G9" t="n">
         <v>-4.1842</v>
@@ -1156,13 +1156,13 @@
         <v>2.4087</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9968</v>
+        <v>-0.3305</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7237</v>
+        <v>0.0165</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2731</v>
+        <v>-0.347</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2022</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.6967</v>
+        <v>-8.4696</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.3458</v>
+        <v>-6.2911</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3509</v>
+        <v>-2.1785</v>
       </c>
       <c r="G10" t="n">
         <v>-6.5884</v>
@@ -1234,13 +1234,13 @@
         <v>2.594</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6635</v>
+        <v>-0.4365</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6727</v>
+        <v>-0.618</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0092</v>
+        <v>0.1815</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2594</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.9869</v>
+        <v>-30.7133</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.1556</v>
+        <v>-10.8822</v>
       </c>
       <c r="F11" t="n">
-        <v>-19.8312</v>
+        <v>-19.8313</v>
       </c>
       <c r="G11" t="n">
         <v>-23.0641</v>
@@ -1291,7 +1291,7 @@
         <v>5.846299999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.574400000000001</v>
+        <v>-2.5744</v>
       </c>
       <c r="M11" t="n">
         <v>-26.3362</v>
@@ -1312,13 +1312,13 @@
         <v>15.7494</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.9035</v>
+        <v>-2.6302</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.267</v>
+        <v>0.00639999999999985</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.6363</v>
+        <v>-2.6365</v>
       </c>
       <c r="V11" t="n">
         <v>-4.0926</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.7554</v>
+        <v>8.775700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>7.2976</v>
+        <v>8.2987</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4579</v>
+        <v>0.477</v>
       </c>
       <c r="G12" t="n">
-        <v>4.0452</v>
+        <v>6.0206</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2769</v>
+        <v>3.4017</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7682</v>
+        <v>2.6189</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1487</v>
+        <v>6.8841</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9413</v>
+        <v>4.2808</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2074</v>
+        <v>2.6033</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1035</v>
+        <v>-0.8635</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6644</v>
+        <v>-0.8791</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5609</v>
+        <v>0.0156</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9691</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4459</v>
+        <v>1.3797</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5232</v>
+        <v>-0.5124</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6294</v>
+        <v>1.8877</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6294</v>
+        <v>1.8877</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.2155</v>
+        <v>7.5484</v>
       </c>
       <c r="E13" t="n">
-        <v>9.278</v>
+        <v>5.339</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0625</v>
+        <v>2.2094</v>
       </c>
       <c r="G13" t="n">
-        <v>6.0206</v>
+        <v>4.0452</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4017</v>
+        <v>3.2769</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6189</v>
+        <v>0.7682</v>
       </c>
       <c r="J13" t="n">
-        <v>6.8841</v>
+        <v>4.1487</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2808</v>
+        <v>3.9413</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6033</v>
+        <v>0.2074</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8635</v>
+        <v>-0.1035</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8791</v>
+        <v>-0.6644</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0156</v>
+        <v>0.5609</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3072</v>
+        <v>1.7621</v>
       </c>
       <c r="T13" t="n">
-        <v>2.359</v>
+        <v>1.4873</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0518</v>
+        <v>0.2748</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8877</v>
+        <v>0.6294</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8877</v>
+        <v>0.6294</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6026</v>
+        <v>6.4943</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4457</v>
+        <v>4.8374</v>
       </c>
       <c r="F14" t="n">
-        <v>1.157</v>
+        <v>1.6569</v>
       </c>
       <c r="G14" t="n">
         <v>7.321</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6802</v>
+        <v>0.2114</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6019</v>
+        <v>-0.2101</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0784</v>
+        <v>0.4215</v>
       </c>
       <c r="V14" t="n">
         <v>0.6294</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3231</v>
+        <v>5.0844</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5776</v>
+        <v>3.006</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7455</v>
+        <v>2.0784</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6117</v>
+        <v>1.4396</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2536</v>
+        <v>-0.184</v>
       </c>
       <c r="I15" t="n">
-        <v>0.358</v>
+        <v>1.6235</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8228</v>
+        <v>1.6971</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3097</v>
+        <v>0.9186</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.487</v>
+        <v>0.7785</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2111</v>
+        <v>-0.2575</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0561</v>
+        <v>-1.1026</v>
       </c>
       <c r="O15" t="n">
         <v>0.845</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2234</v>
+        <v>2.0382</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2234</v>
+        <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0853</v>
+        <v>0.3473</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1816</v>
+        <v>0.0501</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2669</v>
+        <v>0.2972</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5733</v>
+        <v>1.2594</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5733</v>
+        <v>1.2589</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3101</v>
+        <v>4.9273</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3205</v>
+        <v>2.8714</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9896</v>
+        <v>2.0558</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4396</v>
+        <v>0.6117</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.184</v>
+        <v>0.2536</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6235</v>
+        <v>0.358</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6971</v>
+        <v>0.8228</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9186</v>
+        <v>1.3097</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7785</v>
+        <v>-0.487</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2575</v>
+        <v>-0.2111</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1026</v>
+        <v>-1.0561</v>
       </c>
       <c r="O16" t="n">
         <v>0.845</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0382</v>
+        <v>2.2234</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0382</v>
+        <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.427</v>
+        <v>0.5189</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6354</v>
+        <v>0.4754</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2084</v>
+        <v>0.0435</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2594</v>
+        <v>1.5733</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2589</v>
+        <v>1.5733</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6367</v>
+        <v>1.6859</v>
       </c>
       <c r="E18" t="n">
         <v>1.1869</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4498</v>
+        <v>0.4991</v>
       </c>
       <c r="G18" t="n">
         <v>1.3427</v>
@@ -1858,13 +1858,13 @@
         <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0766</v>
+        <v>-0.0274</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2085</v>
+        <v>1.6815</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1175</v>
+        <v>0.5092</v>
       </c>
       <c r="F19" t="n">
-        <v>1.091</v>
+        <v>1.1724</v>
       </c>
       <c r="G19" t="n">
         <v>0.9207</v>
@@ -1936,13 +1936,13 @@
         <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0838</v>
+        <v>0.3892</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2736</v>
+        <v>0.1181</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1897</v>
+        <v>0.2711</v>
       </c>
       <c r="V19" t="n">
         <v>0.0011</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7725</v>
+        <v>0.893</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.156</v>
+        <v>0.3694</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9285</v>
+        <v>0.5236</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1557</v>
+        <v>1.0531</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2989</v>
+        <v>1.4078</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4545</v>
+        <v>-0.3548</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06279999999999999</v>
+        <v>1.2209</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.138</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0829</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0929</v>
+        <v>-0.1678</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2989</v>
+        <v>0.2699</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3917</v>
+        <v>-0.4377</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3706</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2462</v>
+        <v>0.2105</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2189</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4651</v>
+        <v>0.1355</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CALLE GÓMEZ</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6221</v>
+        <v>0.6494</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6221</v>
+        <v>-0.156</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.8054</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6221</v>
+        <v>0.1557</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0.2989</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6221</v>
+        <v>0.4545</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6221</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6221</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.0929</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.2989</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.1231</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.2189</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>A. CALLE GÓMEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3947</v>
+        <v>0.6221</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0756</v>
+        <v>0.6221</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3191</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0531</v>
+        <v>0.6221</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4078</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3548</v>
+        <v>0.6221</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2209</v>
+        <v>0.6221</v>
       </c>
       <c r="K22" t="n">
-        <v>1.138</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0829</v>
+        <v>0.6221</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1678</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2699</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4377</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2878</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2189</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0689</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7534</v>
+        <v>0.2179</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0884</v>
+        <v>-0.4029</v>
       </c>
       <c r="F23" t="n">
-        <v>0.335</v>
+        <v>0.6208</v>
       </c>
       <c r="G23" t="n">
         <v>0.5359</v>
@@ -2248,13 +2248,13 @@
         <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7334000000000001</v>
+        <v>0.2378</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2524</v>
+        <v>0.4331</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.481</v>
+        <v>-0.1952</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.171</v>
+        <v>-2.6791</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2374</v>
+        <v>-4.1394</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0664</v>
+        <v>1.4603</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8323</v>
@@ -2326,13 +2326,13 @@
         <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5245</v>
+        <v>-0.0326</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7113</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1868</v>
+        <v>0.5807</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6289</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8182</v>
+        <v>-4.8434</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4966</v>
+        <v>-4.3987</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3216</v>
+        <v>-0.4447</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0598</v>
@@ -2404,13 +2404,13 @@
         <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2798</v>
+        <v>0.2546</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6081</v>
+        <v>0.485</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>30.98690000000001</v>
+        <v>32.9457</v>
       </c>
       <c r="E26" t="n">
         <v>19.8314</v>
       </c>
       <c r="F26" t="n">
-        <v>11.1557</v>
+        <v>13.1144</v>
       </c>
       <c r="G26" t="n">
         <v>23.0645</v>
@@ -2461,7 +2461,7 @@
         <v>16.8139</v>
       </c>
       <c r="L26" t="n">
-        <v>9.522099999999996</v>
+        <v>9.522099999999998</v>
       </c>
       <c r="M26" t="n">
         <v>-3.2717</v>
@@ -2482,19 +2482,19 @@
         <v>16.676</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9037</v>
+        <v>4.862299999999999</v>
       </c>
       <c r="T26" t="n">
         <v>2.6364</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2670999999999999</v>
+        <v>2.2258</v>
       </c>
       <c r="V26" t="n">
-        <v>4.092500000000001</v>
+        <v>4.0925</v>
       </c>
       <c r="W26" t="n">
-        <v>6.608199999999999</v>
+        <v>6.6082</v>
       </c>
       <c r="X26" t="n">
         <v>-2.5156</v>
